--- a/amitdusane-site-complete/static/templates/adobe-analytics-business-requirements-document-template.xlsx
+++ b/amitdusane-site-complete/static/templates/adobe-analytics-business-requirements-document-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25ed449a1af7f163/Documents/Claude Code/Adobe Analytics/amitdusane-site-complete/static/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F035B759-29D0-421B-87F3-6604B0D3694B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{38535645-991C-484B-A9FB-F1E72974F50C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{3D871C05-C06C-40B4-9302-EE2F7B41902A}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{B8260F1F-8CBE-4BB0-AB64-735EBC1D6878}"/>
   </bookViews>
   <sheets>
     <sheet name="Objectives and Scope" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
     <author>Amit Dusane</author>
   </authors>
   <commentList>
-    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{5C83E4B3-7731-4B13-ACDE-146A0F756902}">
+    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{97960A87-B01E-4C61-A497-9072A0027AD2}">
       <text>
         <r>
           <rPr>
@@ -59,7 +59,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B3" authorId="0" shapeId="0" xr:uid="{210D4CFC-76B7-4CA7-9EE1-F157AF64B3E2}">
+    <comment ref="B3" authorId="0" shapeId="0" xr:uid="{038240EC-EB9F-44EE-AF91-68CC2A0C1F2C}">
       <text>
         <r>
           <rPr>
@@ -73,7 +73,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C3" authorId="0" shapeId="0" xr:uid="{B8673498-8191-46BF-AC76-1E23B4F0ECAB}">
+    <comment ref="C3" authorId="0" shapeId="0" xr:uid="{92790827-3C67-4C2E-88AA-721A4F07C7DA}">
       <text>
         <r>
           <rPr>
@@ -87,7 +87,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{53C22B11-B3BB-421C-B584-9C095E551AF0}">
+    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{A1B7886F-1005-4F8A-977B-AD1275870E5F}">
       <text>
         <r>
           <rPr>
@@ -101,7 +101,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{BA5A7D41-9732-42A8-8948-333D53D5401E}">
+    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{021D59D2-DEA8-46BA-9A3C-8A16A3016D9B}">
       <text>
         <r>
           <rPr>
@@ -115,7 +115,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{D4FFE4B6-F78E-4E3F-B20E-75082D3D2999}">
+    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{88840964-792D-4572-97CE-23A352DABB84}">
       <text>
         <r>
           <rPr>
@@ -129,7 +129,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{7EF1387D-B952-486B-94E3-217DF6B4DB27}">
+    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{7F710BCD-99DA-4B4C-889C-A68B94E29793}">
       <text>
         <r>
           <rPr>
@@ -143,7 +143,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H3" authorId="0" shapeId="0" xr:uid="{8741B8E2-958D-4722-8D1E-53FC33EE5EA4}">
+    <comment ref="H3" authorId="0" shapeId="0" xr:uid="{3DDC2D88-0832-4085-8F27-A29E3D28A0F0}">
       <text>
         <r>
           <rPr>
@@ -157,7 +157,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I3" authorId="0" shapeId="0" xr:uid="{451ABE99-6BE6-4786-8F18-6513D681C5E6}">
+    <comment ref="I3" authorId="0" shapeId="0" xr:uid="{56BCAA95-B741-4893-9E3D-CF59E076AF70}">
       <text>
         <r>
           <rPr>
@@ -171,7 +171,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J3" authorId="0" shapeId="0" xr:uid="{9B17516B-9393-4CE6-B028-BCC4928BB44B}">
+    <comment ref="J3" authorId="0" shapeId="0" xr:uid="{B33D723E-BC7F-4561-80B6-1BCCB14BD74E}">
       <text>
         <r>
           <rPr>
@@ -195,7 +195,7 @@
     <author>Amit Dusane</author>
   </authors>
   <commentList>
-    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{F6F459AE-1B5B-4F90-B217-567ED347FDDE}">
+    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{35CFB32B-8091-4BB9-8CB9-7F13EDACCF15}">
       <text>
         <r>
           <rPr>
@@ -209,7 +209,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B3" authorId="0" shapeId="0" xr:uid="{1652414E-6875-4F86-93C1-DB6C07E48F69}">
+    <comment ref="B3" authorId="0" shapeId="0" xr:uid="{D274F16E-4F50-4FF5-9B3F-E67D2C2BCEA3}">
       <text>
         <r>
           <rPr>
@@ -223,7 +223,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C3" authorId="0" shapeId="0" xr:uid="{2C28FBA0-ACCE-45DA-B793-FC5C45E825A6}">
+    <comment ref="C3" authorId="0" shapeId="0" xr:uid="{00B249DE-7C26-44AE-8C6D-F766564AFA56}">
       <text>
         <r>
           <rPr>
@@ -237,7 +237,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{53162EE0-3BB9-4C9B-9313-173E3CF551FA}">
+    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{37868621-C861-4E60-938F-259BA2FFE515}">
       <text>
         <r>
           <rPr>
@@ -256,7 +256,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="255">
   <si>
     <t>Kestrel and Co. - Business Requirements Document - Objectives and Scope</t>
   </si>
@@ -972,10 +972,7 @@
     <t>What changed and why</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>2026-03-02</t>
+    <t>02 Mar 2026</t>
   </si>
   <si>
     <t>1.0 draft</t>
@@ -987,10 +984,7 @@
     <t>First draft circulated after the discovery workshop.</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
+    <t>09 Mar 2026</t>
   </si>
   <si>
     <t>KES-R015, KES-R026, KES-R027, KES-R035, KES-R036</t>
@@ -999,10 +993,7 @@
     <t>Five recommended requirements added. None of these were asked for. All five were accepted.</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>2026-03-11</t>
+    <t>11 Mar 2026</t>
   </si>
   <si>
     <t>KES-R016 to KES-R020, KES-R028, KES-R031</t>
@@ -1011,10 +1002,7 @@
     <t>Moved to Phase 2 after the effort estimate. Agreed on the call of 11 March.</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>2026-03-13</t>
+    <t>13 Mar 2026</t>
   </si>
   <si>
     <t>KES-X001 to KES-X006</t>
@@ -1023,10 +1011,7 @@
     <t>Out of Scope sheet added. Four items came out of the requirements list, two were raised in the workshop and had nowhere else to live.</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>2026-03-16</t>
+    <t>16 Mar 2026</t>
   </si>
   <si>
     <t>1.0</t>
@@ -1035,7 +1020,7 @@
     <t>All</t>
   </si>
   <si>
-    <t>Signed off by Kestrel and Co. except KES-R018, which is queried and stays in Phase 2.</t>
+    <t>Signed off by the Kestrel business team except KES-R018, which is queried and stays in Phase 2.</t>
   </si>
 </sst>
 </file>
@@ -1115,9 +1100,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1438,7 +1430,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C91E56E-65EB-472E-A6AF-F728A1A26046}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF1456B1-159E-48D3-9E12-35011F3DC08E}">
   <sheetPr>
     <tabColor rgb="FFEDA50D"/>
   </sheetPr>
@@ -1601,7 +1593,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDB2A951-3788-4E02-8339-C1100221F37F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7E637F6-A701-4FFB-B90A-84193B96CC2E}">
   <sheetPr>
     <tabColor rgb="FFEDA50D"/>
   </sheetPr>
@@ -2810,14 +2802,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J39" xr:uid="{BDB2A951-3788-4E02-8339-C1100221F37F}"/>
+  <autoFilter ref="A3:J39" xr:uid="{A7E637F6-A701-4FFB-B90A-84193B96CC2E}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBA71920-43F3-4302-AC0F-F2811DD33B0F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2B897CC-5D44-488D-86A9-2D5B2E4124B9}">
   <sheetPr>
     <tabColor rgb="FFD04646"/>
   </sheetPr>
@@ -2941,7 +2933,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D607325-98CE-4F80-A1C2-0DF032F17F42}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA41A479-0EA7-4C44-9CA4-1EA13DE7E97A}">
   <sheetPr>
     <tabColor rgb="FFA6A6A6"/>
   </sheetPr>
@@ -2949,8 +2941,8 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.59765625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="14.59765625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="12.59765625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="14.59765625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="12.59765625" style="5" customWidth="1"/>
     <col min="4" max="4" width="16.59765625" style="2" customWidth="1"/>
     <col min="5" max="5" width="72.59765625" style="2" customWidth="1"/>
     <col min="6" max="16384" width="9.06640625" style="2"/>
@@ -2965,10 +2957,10 @@
       <c r="A3" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="6" t="s">
         <v>235</v>
       </c>
       <c r="D3" s="3" t="s">
@@ -2979,88 +2971,88 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="4">
+        <v>1</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="C4" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="E4" s="4" t="s">
+    </row>
+    <row r="5" spans="1:5" ht="57" x14ac:dyDescent="0.45">
+      <c r="A5" s="4">
+        <v>2</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="57" x14ac:dyDescent="0.45">
-      <c r="A5" s="4" t="s">
+      <c r="C5" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="E5" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="D5" s="4" t="s">
+    </row>
+    <row r="6" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A6" s="4">
+        <v>3</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="C6" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="B6" s="4" t="s">
+    </row>
+    <row r="7" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A7" s="4">
+        <v>4</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="D6" s="4" t="s">
+      <c r="C7" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E7" s="4" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A7" s="4" t="s">
+    <row r="8" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A8" s="4">
+        <v>5</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="C8" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="D7" s="4" t="s">
+      <c r="D8" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E8" s="4" t="s">
         <v>254</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A8" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>259</v>
       </c>
     </row>
   </sheetData>

--- a/amitdusane-site-complete/static/templates/adobe-analytics-business-requirements-document-template.xlsx
+++ b/amitdusane-site-complete/static/templates/adobe-analytics-business-requirements-document-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25ed449a1af7f163/Documents/Claude Code/Adobe Analytics/amitdusane-site-complete/static/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{38535645-991C-484B-A9FB-F1E72974F50C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5D03CE3D-59FB-43BD-89EF-D251BF29B963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{B8260F1F-8CBE-4BB0-AB64-735EBC1D6878}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{04DC12EB-FE89-4AE7-AE5A-759D53E446EC}"/>
   </bookViews>
   <sheets>
     <sheet name="Objectives and Scope" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
     <author>Amit Dusane</author>
   </authors>
   <commentList>
-    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{97960A87-B01E-4C61-A497-9072A0027AD2}">
+    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{BD337EFA-917E-4FA5-935D-827B376284CE}">
       <text>
         <r>
           <rPr>
@@ -59,7 +59,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B3" authorId="0" shapeId="0" xr:uid="{038240EC-EB9F-44EE-AF91-68CC2A0C1F2C}">
+    <comment ref="B3" authorId="0" shapeId="0" xr:uid="{6CB3CB6A-DEC4-4918-9887-B9AFBE53048E}">
       <text>
         <r>
           <rPr>
@@ -73,7 +73,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C3" authorId="0" shapeId="0" xr:uid="{92790827-3C67-4C2E-88AA-721A4F07C7DA}">
+    <comment ref="C3" authorId="0" shapeId="0" xr:uid="{E65E4BF7-88A9-4F4C-8782-6872F129323B}">
       <text>
         <r>
           <rPr>
@@ -87,7 +87,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{A1B7886F-1005-4F8A-977B-AD1275870E5F}">
+    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{5CD48955-B8AA-4761-A768-7309430EEE58}">
       <text>
         <r>
           <rPr>
@@ -101,7 +101,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{021D59D2-DEA8-46BA-9A3C-8A16A3016D9B}">
+    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{CD4B6030-A2F5-4426-8FEA-97115E0F5956}">
       <text>
         <r>
           <rPr>
@@ -115,7 +115,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{88840964-792D-4572-97CE-23A352DABB84}">
+    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{0CF2327F-887A-42D4-8BE5-063B237EBFD7}">
       <text>
         <r>
           <rPr>
@@ -129,7 +129,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{7F710BCD-99DA-4B4C-889C-A68B94E29793}">
+    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{BB984006-EEC7-4ABD-AFA5-F63E35399FE6}">
       <text>
         <r>
           <rPr>
@@ -143,7 +143,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H3" authorId="0" shapeId="0" xr:uid="{3DDC2D88-0832-4085-8F27-A29E3D28A0F0}">
+    <comment ref="H3" authorId="0" shapeId="0" xr:uid="{3DE4F13C-1519-4615-AF8E-F7BEA90F50A4}">
       <text>
         <r>
           <rPr>
@@ -157,7 +157,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I3" authorId="0" shapeId="0" xr:uid="{56BCAA95-B741-4893-9E3D-CF59E076AF70}">
+    <comment ref="I3" authorId="0" shapeId="0" xr:uid="{EC181BAB-7126-41AB-AF73-1ADB3B45B391}">
       <text>
         <r>
           <rPr>
@@ -171,7 +171,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J3" authorId="0" shapeId="0" xr:uid="{B33D723E-BC7F-4561-80B6-1BCCB14BD74E}">
+    <comment ref="J3" authorId="0" shapeId="0" xr:uid="{1A8BC208-DB73-4DB9-851D-21C20A239E1D}">
       <text>
         <r>
           <rPr>
@@ -195,7 +195,7 @@
     <author>Amit Dusane</author>
   </authors>
   <commentList>
-    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{35CFB32B-8091-4BB9-8CB9-7F13EDACCF15}">
+    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{81AD04E7-C64C-48B8-AB51-0CC9E0A2FDE2}">
       <text>
         <r>
           <rPr>
@@ -209,7 +209,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B3" authorId="0" shapeId="0" xr:uid="{D274F16E-4F50-4FF5-9B3F-E67D2C2BCEA3}">
+    <comment ref="B3" authorId="0" shapeId="0" xr:uid="{FA25F101-9320-43F1-A81A-60B2F8C5A9F2}">
       <text>
         <r>
           <rPr>
@@ -223,7 +223,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C3" authorId="0" shapeId="0" xr:uid="{00B249DE-7C26-44AE-8C6D-F766564AFA56}">
+    <comment ref="C3" authorId="0" shapeId="0" xr:uid="{634CB7A7-BFF5-473C-A54B-0A8ED655F2AC}">
       <text>
         <r>
           <rPr>
@@ -237,7 +237,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{37868621-C861-4E60-938F-259BA2FFE515}">
+    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{9D557695-5BD3-4228-9766-BC6724A14521}">
       <text>
         <r>
           <rPr>
@@ -256,7 +256,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="256">
   <si>
     <t>Kestrel and Co. - Business Requirements Document - Objectives and Scope</t>
   </si>
@@ -346,6 +346,9 @@
   </si>
   <si>
     <t>Behavioural depth: filtering, sorting, reviews, wishlist, imagery. Scoped after Phase 1 is live.</t>
+  </si>
+  <si>
+    <t>Template from amitdusane.com  |  Amit G Dusane</t>
   </si>
   <si>
     <t>Kestrel and Co. - Business Requirements - Website - Version 1.0</t>
@@ -1027,7 +1030,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1047,6 +1050,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF808080"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1100,7 +1111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1110,6 +1121,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1430,11 +1442,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF1456B1-159E-48D3-9E12-35011F3DC08E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38AD41DF-D33F-41F6-B815-FF195E864186}">
   <sheetPr>
     <tabColor rgb="FFEDA50D"/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="16.59765625" style="2" customWidth="1"/>
@@ -1587,17 +1599,25 @@
       </c>
       <c r="C17" s="4"/>
     </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A19" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;"Calibri"&amp;8&amp;K808080Template from amitdusane.com   |   Amit G Dusane&amp;R&amp;"Calibri"&amp;8&amp;K808080Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7E637F6-A701-4FFB-B90A-84193B96CC2E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D8EA101-632E-49B8-9C52-4B9DE47C2560}">
   <sheetPr>
     <tabColor rgb="FFEDA50D"/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14.59765625" style="2" customWidth="1"/>
@@ -1614,1206 +1634,1214 @@
   <sheetData>
     <row r="1" spans="1:10" ht="16.899999999999999" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A4" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>4</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>26</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A5" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>26</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A6" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>26</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>4</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>26</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A8" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>4</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I8" s="4" t="s">
         <v>26</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A9" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>4</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>26</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A10" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>4</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I10" s="4" t="s">
         <v>26</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A11" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>4</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I11" s="4" t="s">
         <v>26</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A12" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>4</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I12" s="4" t="s">
         <v>26</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A13" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I13" s="4" t="s">
         <v>26</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A14" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>4</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I14" s="4" t="s">
         <v>26</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A15" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>4</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I15" s="4" t="s">
         <v>26</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A16" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I16" s="4" t="s">
         <v>26</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A17" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I17" s="4" t="s">
         <v>26</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A18" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I18" s="4" t="s">
         <v>26</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A19" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I19" s="4" t="s">
         <v>28</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A20" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I20" s="4" t="s">
         <v>28</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A21" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I21" s="4" t="s">
         <v>28</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A22" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I22" s="4" t="s">
         <v>28</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A23" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I23" s="4" t="s">
         <v>28</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A24" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I24" s="4" t="s">
         <v>26</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A25" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I25" s="4" t="s">
         <v>26</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A26" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I26" s="4" t="s">
         <v>26</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A27" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I27" s="4" t="s">
         <v>26</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A28" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I28" s="4" t="s">
         <v>26</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A29" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I29" s="4" t="s">
         <v>26</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A30" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I30" s="4" t="s">
         <v>26</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A31" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I31" s="4" t="s">
         <v>28</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A32" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I32" s="4" t="s">
         <v>26</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A33" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I33" s="4" t="s">
         <v>26</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A34" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I34" s="4" t="s">
         <v>28</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A35" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I35" s="4" t="s">
         <v>26</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A36" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I36" s="4" t="s">
         <v>26</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A37" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I37" s="4" t="s">
         <v>26</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A38" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D38" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="G38" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="E38" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="G38" s="4" t="s">
-        <v>195</v>
-      </c>
       <c r="H38" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I38" s="4" t="s">
         <v>26</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A39" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I39" s="4" t="s">
         <v>26</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A41" s="5" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J39" xr:uid="{A7E637F6-A701-4FFB-B90A-84193B96CC2E}"/>
+  <autoFilter ref="A3:J39" xr:uid="{2D8EA101-632E-49B8-9C52-4B9DE47C2560}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;"Calibri"&amp;8&amp;K808080Template from amitdusane.com   |   Amit G Dusane&amp;R&amp;"Calibri"&amp;8&amp;K808080Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2B897CC-5D44-488D-86A9-2D5B2E4124B9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2FFB137-08BF-4CA5-BD2A-BB83BB859944}">
   <sheetPr>
     <tabColor rgb="FFD04646"/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14.59765625" style="2" customWidth="1"/>
@@ -2825,124 +2853,132 @@
   <sheetData>
     <row r="1" spans="1:4" ht="16.899999999999999" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A4" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A5" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A6" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A7" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="57" x14ac:dyDescent="0.45">
       <c r="A8" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="57" x14ac:dyDescent="0.45">
       <c r="A9" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A11" s="5" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;"Calibri"&amp;8&amp;K808080Template from amitdusane.com   |   Amit G Dusane&amp;R&amp;"Calibri"&amp;8&amp;K808080Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA41A479-0EA7-4C44-9CA4-1EA13DE7E97A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F880EAFB-FA53-459D-8B81-40A46C16A6A0}">
   <sheetPr>
     <tabColor rgb="FFA6A6A6"/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.59765625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="14.59765625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="12.59765625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="14.59765625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="12.59765625" style="6" customWidth="1"/>
     <col min="4" max="4" width="16.59765625" style="2" customWidth="1"/>
     <col min="5" max="5" width="72.59765625" style="2" customWidth="1"/>
     <col min="6" max="16384" width="9.06640625" style="2"/>
@@ -2950,112 +2986,120 @@
   <sheetData>
     <row r="1" spans="1:5" ht="16.899999999999999" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="B3" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>235</v>
       </c>
+      <c r="C3" s="7" t="s">
+        <v>236</v>
+      </c>
       <c r="D3" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="4">
         <v>1</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>238</v>
-      </c>
-      <c r="C4" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>239</v>
       </c>
+      <c r="C4" s="8" t="s">
+        <v>240</v>
+      </c>
       <c r="D4" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A5" s="4">
         <v>2</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>239</v>
+      <c r="B5" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>240</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A6" s="4">
         <v>3</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>239</v>
+      <c r="B6" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>240</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A7" s="4">
         <v>4</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>239</v>
+      <c r="B7" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>240</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A8" s="4">
         <v>5</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="C8" s="7" t="s">
+      <c r="B8" s="8" t="s">
         <v>252</v>
       </c>
+      <c r="C8" s="8" t="s">
+        <v>253</v>
+      </c>
       <c r="D8" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A10" s="5" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;"Calibri"&amp;8&amp;K808080Template from amitdusane.com   |   Amit G Dusane&amp;R&amp;"Calibri"&amp;8&amp;K808080Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>